--- a/logs/encoders/best_configurations_seed42.xlsx
+++ b/logs/encoders/best_configurations_seed42.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddore/Documents/RooseBERT/logs/encoders/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7282B8F9-E971-B149-AC80-D03DF1AEF415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82D5907-7293-094B-9688-830377743C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4700" yWindow="660" windowWidth="28040" windowHeight="17440" xr2:uid="{6ADC44A3-5965-4043-91E7-6BE1CD1C48A4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" activeTab="2" xr2:uid="{6ADC44A3-5965-4043-91E7-6BE1CD1C48A4}"/>
   </bookViews>
   <sheets>
     <sheet name="argument detection" sheetId="1" r:id="rId1"/>
     <sheet name="relation classification" sheetId="3" r:id="rId2"/>
+    <sheet name="sentiment analysis" sheetId="4" r:id="rId3"/>
+    <sheet name="stance detection" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="94">
   <si>
     <t>run</t>
   </si>
@@ -235,6 +237,90 @@
   </si>
   <si>
     <t>RooseBERT-scr-uncased-EPOCH3-LR2e-5-WD0.1-B16-ML512</t>
+  </si>
+  <si>
+    <t>RooseBERT-large-scr-uncased-EPOCH2-LR2e-5-WD0.01-B32-ML256</t>
+  </si>
+  <si>
+    <t>RooseBERT-large-scr-cased-EPOCH2-LR2e-5-WD0.01-B16-ML256</t>
+  </si>
+  <si>
+    <t>RooseBERT-large-cont-uncased-EPOCH3-LR2e-5-WD0.01-B32-ML256</t>
+  </si>
+  <si>
+    <t>RooseBERT-large-cont-cased-EPOCH3-LR2e-5-WD0.01-B16-ML256</t>
+  </si>
+  <si>
+    <t>bert-large-uncased-EPOCH2-LR2e-5-WD0.01-B8-ML512</t>
+  </si>
+  <si>
+    <t>bert-large-cased-EPOCH3-LR2e-5-WD0.01-B8-ML512</t>
+  </si>
+  <si>
+    <t>bert-base-cased-EPOCH4-LR3e-5-WD0.01-B16</t>
+  </si>
+  <si>
+    <t>bert-base-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
+  </si>
+  <si>
+    <t>ConfliBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B8</t>
+  </si>
+  <si>
+    <t>ConfliBERT-cont-uncased-EPOCH3-LR3e-5-WD0.01-B32</t>
+  </si>
+  <si>
+    <t>ConfliBERT-scr-cased-EPOCH2-LR2e-5-WD0.01-B32</t>
+  </si>
+  <si>
+    <t>ConfliBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B8</t>
+  </si>
+  <si>
+    <t>polibertweet-political-twitter-roberta-mlm-EPOCH4-LR2e-5-WD0.01-B8</t>
+  </si>
+  <si>
+    <t>RooseBERT-cont-cased-EPOCH4-LR2e-5-WD0.01-B16</t>
+  </si>
+  <si>
+    <t>RooseBERT-cont-uncased-EPOCH3-LR3e-5-WD0.01-B8</t>
+  </si>
+  <si>
+    <t>RooseBERT-scr-cased-EPOCH4-LR5e-5-WD0.01-B32</t>
+  </si>
+  <si>
+    <t>RooseBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B8</t>
+  </si>
+  <si>
+    <t>bert-base-cased-EPOCH3-LR2e-5-WD0.01-B32</t>
+  </si>
+  <si>
+    <t>bert-base-uncased-EPOCH4-LR3e-5-WD0.01-B32</t>
+  </si>
+  <si>
+    <t>ConfliBERT-cont-cased-EPOCH4-LR3e-5-WD0.01-B32</t>
+  </si>
+  <si>
+    <t>ConfliBERT-cont-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
+  </si>
+  <si>
+    <t>ConfliBERT-scr-cased-EPOCH2-LR2e-5-WD0.01-B8</t>
+  </si>
+  <si>
+    <t>ConfliBERT-scr-uncased-EPOCH4-LR3e-5-WD0.01-B32</t>
+  </si>
+  <si>
+    <t>polibertweet-political-twitter-roberta-mlm-EPOCH3-LR2e-5-WD0.01-B16</t>
+  </si>
+  <si>
+    <t>RooseBERT-cont-cased-EPOCH2-LR3e-5-WD0.01-B16</t>
+  </si>
+  <si>
+    <t>RooseBERT-cont-uncased-EPOCH4-LR3e-5-WD0.01-B16</t>
+  </si>
+  <si>
+    <t>RooseBERT-scr-cased-EPOCH3-LR3e-5-WD0.01-B16</t>
+  </si>
+  <si>
+    <t>RooseBERT-scr-uncased-EPOCH3-LR3e-5-WD0.01-B32</t>
   </si>
 </sst>
 </file>
@@ -269,7 +355,7 @@
       <name val="Calibri (Corpo)"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -282,8 +368,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8D3EF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -306,11 +398,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -323,6 +428,15 @@
     <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1963,4 +2077,1098 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9804E628-FA83-7849-89EC-04C032EE7190}">
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="67.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="6">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6">
+        <v>8</v>
+      </c>
+      <c r="F2" s="7">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0.69117934676315296</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0.52809324566646743</v>
+      </c>
+      <c r="J2" s="6">
+        <v>1</v>
+      </c>
+      <c r="K2" s="6">
+        <v>0.52809324566646743</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="6">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6">
+        <v>8</v>
+      </c>
+      <c r="F3" s="7">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0.69131455399061004</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0.52825112107623318</v>
+      </c>
+      <c r="J3" s="6">
+        <v>1</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0.52839210998206809</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="6">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0.72522522522522526</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.72156862745098038</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0.72891907187323146</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0.70830842797369997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6">
+        <v>3</v>
+      </c>
+      <c r="E5" s="6">
+        <v>32</v>
+      </c>
+      <c r="F5" s="7">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0.72326165875453785</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0.71389195148842333</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0.73288058856819471</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0.7038254632396892</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="6">
+        <v>2</v>
+      </c>
+      <c r="E6" s="6">
+        <v>16</v>
+      </c>
+      <c r="F6" s="7">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.72377338031986993</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0.69458896982310092</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0.75551782682512736</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0.69545726240286909</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="6">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6">
+        <v>32</v>
+      </c>
+      <c r="F7" s="7">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.72673160173160178</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.69621565578019695</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0.76004527447651382</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0.69814704124327553</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="6">
+        <v>3</v>
+      </c>
+      <c r="E8" s="6">
+        <v>32</v>
+      </c>
+      <c r="F8" s="6">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.63375702039609816</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.6633663366336634</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.60667798528579508</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0.62970711297071125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="6">
+        <v>4</v>
+      </c>
+      <c r="E9" s="6">
+        <v>32</v>
+      </c>
+      <c r="F9" s="6">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.66774541531823084</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.63781555899021125</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0.7006225240520656</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0.63179916317991636</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="6">
+        <v>4</v>
+      </c>
+      <c r="E10" s="6">
+        <v>32</v>
+      </c>
+      <c r="F10" s="6">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.68342276193165774</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0.68207440811724918</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0.68477645727221281</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0.66497310221159589</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="6">
+        <v>4</v>
+      </c>
+      <c r="E11" s="6">
+        <v>16</v>
+      </c>
+      <c r="F11" s="6">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.65727429557216788</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0.66803039158386912</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0.64685908319185059</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0.64375373580394502</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="6">
+        <v>2</v>
+      </c>
+      <c r="E12" s="6">
+        <v>8</v>
+      </c>
+      <c r="F12" s="6">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0.69483315392895584</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0.66239096972806566</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0.73061686474250143</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0.66108786610878656</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="6">
+        <v>4</v>
+      </c>
+      <c r="E13" s="6">
+        <v>32</v>
+      </c>
+      <c r="F13" s="6">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0.69989165763813654</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0.67116883116883119</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0.73118279569892475</v>
+      </c>
+      <c r="K13" s="6">
+        <v>0.66885833831440522</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="6">
+        <v>3</v>
+      </c>
+      <c r="E14" s="6">
+        <v>16</v>
+      </c>
+      <c r="F14" s="6">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0.649850827230811</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0.62395833333333328</v>
+      </c>
+      <c r="J14" s="6">
+        <v>0.67798528579513295</v>
+      </c>
+      <c r="K14" s="6">
+        <v>0.61416616855947403</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="6">
+        <v>2</v>
+      </c>
+      <c r="E15" s="6">
+        <v>16</v>
+      </c>
+      <c r="F15" s="6">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0.73555259653794935</v>
+      </c>
+      <c r="I15" s="6">
+        <v>0.69466800804828976</v>
+      </c>
+      <c r="J15" s="6">
+        <v>0.78155065082059993</v>
+      </c>
+      <c r="K15" s="6">
+        <v>0.70322773460848775</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="6">
+        <v>4</v>
+      </c>
+      <c r="E16" s="6">
+        <v>16</v>
+      </c>
+      <c r="F16" s="6">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H16" s="6">
+        <v>0.7262662607251591</v>
+      </c>
+      <c r="I16" s="6">
+        <v>0.71072589382448537</v>
+      </c>
+      <c r="J16" s="6">
+        <v>0.74250141482739107</v>
+      </c>
+      <c r="K16" s="6">
+        <v>0.70442319187089064</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="6">
+        <v>3</v>
+      </c>
+      <c r="E17" s="6">
+        <v>16</v>
+      </c>
+      <c r="F17" s="6">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0.73459459459459464</v>
+      </c>
+      <c r="I17" s="6">
+        <v>0.7030522503879979</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0.76910016977928697</v>
+      </c>
+      <c r="K17" s="6">
+        <v>0.70651524208009564</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="6">
+        <v>3</v>
+      </c>
+      <c r="E18" s="6">
+        <v>32</v>
+      </c>
+      <c r="F18" s="6">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H18" s="6">
+        <v>0.72555555555555551</v>
+      </c>
+      <c r="I18" s="6">
+        <v>0.71249318057828692</v>
+      </c>
+      <c r="J18" s="6">
+        <v>0.73910582908885114</v>
+      </c>
+      <c r="K18" s="6">
+        <v>0.70472205618649131</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A116D17-9AF7-4A4D-9D05-399661DEEF71}">
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="70.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="19" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="6">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6">
+        <v>16</v>
+      </c>
+      <c r="F2" s="6">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0.41441718813238498</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0.4142492276463568</v>
+      </c>
+      <c r="J2" s="6">
+        <v>0.4333473137689583</v>
+      </c>
+      <c r="K2" s="6">
+        <v>0.42881529532263568</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="6">
+        <v>4</v>
+      </c>
+      <c r="E3" s="6">
+        <v>16</v>
+      </c>
+      <c r="F3" s="6">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0.42366016590260508</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0.42358866008649881</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0.43150066910983859</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0.42744964151587572</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="6">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6">
+        <v>8</v>
+      </c>
+      <c r="F4" s="6">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0.42524913978187501</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.4247112605893581</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0.44557574829216451</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0.44076476613178561</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6">
+        <v>3</v>
+      </c>
+      <c r="E5" s="6">
+        <v>32</v>
+      </c>
+      <c r="F5" s="6">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0.42790851372527677</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0.42696825589163162</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0.44649850189562962</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0.44144759303516562</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="6">
+        <v>2</v>
+      </c>
+      <c r="E6" s="6">
+        <v>32</v>
+      </c>
+      <c r="F6" s="6">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.4307734120372857</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0.43055164759283238</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0.447254652841025</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0.44213041993854563</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="6">
+        <v>4</v>
+      </c>
+      <c r="E7" s="6">
+        <v>8</v>
+      </c>
+      <c r="F7" s="6">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.42919201447356597</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.42840675369380499</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0.44762233515830713</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0.44315466029361561</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="6">
+        <v>4</v>
+      </c>
+      <c r="E8" s="6">
+        <v>8</v>
+      </c>
+      <c r="F8" s="6">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.43729616908896429</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.44091490823207902</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.44859508462953768</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0.44349607374530559</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="6">
+        <v>4</v>
+      </c>
+      <c r="E9" s="6">
+        <v>16</v>
+      </c>
+      <c r="F9" s="6">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.42420684743682457</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.42592016793038268</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0.44397123742230621</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0.43871628542164559</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="6">
+        <v>3</v>
+      </c>
+      <c r="E10" s="6">
+        <v>8</v>
+      </c>
+      <c r="F10" s="6">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.43572755479480257</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0.43737034395009322</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0.46113800315406173</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0.45646978490952539</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="6">
+        <v>4</v>
+      </c>
+      <c r="E11" s="6">
+        <v>32</v>
+      </c>
+      <c r="F11" s="6">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.42282602623570131</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0.42303761452812361</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0.43202268431307123</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0.42813246841925567</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6">
+        <v>4</v>
+      </c>
+      <c r="E12" s="6">
+        <v>8</v>
+      </c>
+      <c r="F12" s="6">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0.43165791366051121</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0.4330795209717142</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0.45850326738972208</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0.45339706384431538</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/logs/encoders/best_configurations_seed42.xlsx
+++ b/logs/encoders/best_configurations_seed42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddore/Documents/RooseBERT/logs/encoders/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82D5907-7293-094B-9688-830377743C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08992CBC-A170-D74E-88A6-B606C6F2A484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" activeTab="2" xr2:uid="{6ADC44A3-5965-4043-91E7-6BE1CD1C48A4}"/>
   </bookViews>

--- a/logs/encoders/best_configurations_seed42.xlsx
+++ b/logs/encoders/best_configurations_seed42.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddore/Documents/RooseBERT/logs/encoders/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08992CBC-A170-D74E-88A6-B606C6F2A484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0077066C-14E9-954C-A714-A39D56EFA3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" activeTab="2" xr2:uid="{6ADC44A3-5965-4043-91E7-6BE1CD1C48A4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" activeTab="3" xr2:uid="{6ADC44A3-5965-4043-91E7-6BE1CD1C48A4}"/>
   </bookViews>
   <sheets>
     <sheet name="argument detection" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="100">
   <si>
     <t>run</t>
   </si>
@@ -321,6 +321,24 @@
   </si>
   <si>
     <t>RooseBERT-scr-uncased-EPOCH3-LR3e-5-WD0.01-B32</t>
+  </si>
+  <si>
+    <t>bert-large-cased-EPOCH4-LR3e-5-WD0.01-B32</t>
+  </si>
+  <si>
+    <t>bert-large-uncased-EPOCH2-LR2e-5-WD0.01-B32</t>
+  </si>
+  <si>
+    <t>RooseBERT-large-cont-cased-EPOCH4-LR2e-5-WD0.01-B8</t>
+  </si>
+  <si>
+    <t>RooseBERT-large-cont-uncased-EPOCH4-LR2e-5-WD0.01-B16</t>
+  </si>
+  <si>
+    <t>RooseBERT-large-scr-cased-EPOCH4-LR2e-5-WD0.01-B32</t>
+  </si>
+  <si>
+    <t>RooseBERT-large-scr-uncased-EPOCH4-LR2e-5-WD0.01-B8</t>
   </si>
 </sst>
 </file>
@@ -415,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -437,6 +455,7 @@
     <xf numFmtId="11" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -2733,7 +2752,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A116D17-9AF7-4A4D-9D05-399661DEEF71}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.1640625" bestFit="1" customWidth="1"/>
@@ -2741,7 +2760,7 @@
     <col min="3" max="3" width="8.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
@@ -2799,7 +2818,7 @@
       <c r="E2" s="6">
         <v>16</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="7">
         <v>3.0000000000000001E-5</v>
       </c>
       <c r="G2" s="6">
@@ -2834,7 +2853,7 @@
       <c r="E3" s="6">
         <v>16</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="7">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="G3" s="6">
@@ -2855,10 +2874,10 @@
     </row>
     <row r="4" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>16</v>
@@ -2867,243 +2886,243 @@
         <v>4</v>
       </c>
       <c r="E4" s="6">
-        <v>8</v>
-      </c>
-      <c r="F4" s="6">
-        <v>2.0000000000000002E-5</v>
+        <v>32</v>
+      </c>
+      <c r="F4" s="7">
+        <v>3.0000000000000001E-5</v>
       </c>
       <c r="G4" s="6">
         <v>0.01</v>
       </c>
       <c r="H4" s="6">
-        <v>0.42524913978187501</v>
+        <v>0.41679754592918761</v>
       </c>
       <c r="I4" s="6">
-        <v>0.4247112605893581</v>
+        <v>0.42885107338015938</v>
       </c>
       <c r="J4" s="6">
-        <v>0.44557574829216451</v>
+        <v>0.44896675520583751</v>
       </c>
       <c r="K4" s="6">
-        <v>0.44076476613178561</v>
+        <v>0.44281324684192558</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="6">
         <v>32</v>
       </c>
-      <c r="F5" s="6">
-        <v>3.0000000000000001E-5</v>
+      <c r="F5" s="7">
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="G5" s="6">
         <v>0.01</v>
       </c>
       <c r="H5" s="6">
-        <v>0.42790851372527677</v>
+        <v>0.38070257741152908</v>
       </c>
       <c r="I5" s="6">
-        <v>0.42696825589163162</v>
+        <v>0.4056787310573795</v>
       </c>
       <c r="J5" s="6">
-        <v>0.44649850189562962</v>
+        <v>0.43746673501785521</v>
       </c>
       <c r="K5" s="6">
-        <v>0.44144759303516562</v>
+        <v>0.4308637760327757</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" s="6">
-        <v>32</v>
-      </c>
-      <c r="F6" s="6">
+        <v>8</v>
+      </c>
+      <c r="F6" s="7">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="G6" s="6">
         <v>0.01</v>
       </c>
       <c r="H6" s="6">
-        <v>0.4307734120372857</v>
+        <v>0.42524913978187501</v>
       </c>
       <c r="I6" s="6">
-        <v>0.43055164759283238</v>
+        <v>0.4247112605893581</v>
       </c>
       <c r="J6" s="6">
-        <v>0.447254652841025</v>
+        <v>0.44557574829216451</v>
       </c>
       <c r="K6" s="6">
-        <v>0.44213041993854563</v>
+        <v>0.44076476613178561</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="6">
-        <v>8</v>
-      </c>
-      <c r="F7" s="6">
+        <v>32</v>
+      </c>
+      <c r="F7" s="7">
         <v>3.0000000000000001E-5</v>
       </c>
       <c r="G7" s="6">
         <v>0.01</v>
       </c>
       <c r="H7" s="6">
-        <v>0.42919201447356597</v>
+        <v>0.42790851372527677</v>
       </c>
       <c r="I7" s="6">
-        <v>0.42840675369380499</v>
+        <v>0.42696825589163162</v>
       </c>
       <c r="J7" s="6">
-        <v>0.44762233515830713</v>
+        <v>0.44649850189562962</v>
       </c>
       <c r="K7" s="6">
-        <v>0.44315466029361561</v>
+        <v>0.44144759303516562</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D8" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="6">
-        <v>8</v>
-      </c>
-      <c r="F8" s="6">
+        <v>32</v>
+      </c>
+      <c r="F8" s="7">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="G8" s="6">
         <v>0.01</v>
       </c>
       <c r="H8" s="6">
-        <v>0.43729616908896429</v>
+        <v>0.4307734120372857</v>
       </c>
       <c r="I8" s="6">
-        <v>0.44091490823207902</v>
+        <v>0.43055164759283238</v>
       </c>
       <c r="J8" s="6">
-        <v>0.44859508462953768</v>
+        <v>0.447254652841025</v>
       </c>
       <c r="K8" s="6">
-        <v>0.44349607374530559</v>
+        <v>0.44213041993854563</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D9" s="6">
         <v>4</v>
       </c>
       <c r="E9" s="6">
-        <v>16</v>
-      </c>
-      <c r="F9" s="6">
-        <v>2.0000000000000002E-5</v>
+        <v>8</v>
+      </c>
+      <c r="F9" s="7">
+        <v>3.0000000000000001E-5</v>
       </c>
       <c r="G9" s="6">
         <v>0.01</v>
       </c>
       <c r="H9" s="6">
-        <v>0.42420684743682457</v>
+        <v>0.42919201447356597</v>
       </c>
       <c r="I9" s="6">
-        <v>0.42592016793038268</v>
+        <v>0.42840675369380499</v>
       </c>
       <c r="J9" s="6">
-        <v>0.44397123742230621</v>
+        <v>0.44762233515830713</v>
       </c>
       <c r="K9" s="6">
-        <v>0.43871628542164559</v>
+        <v>0.44315466029361561</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="D10" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="6">
         <v>8</v>
       </c>
-      <c r="F10" s="6">
-        <v>3.0000000000000001E-5</v>
+      <c r="F10" s="7">
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="G10" s="6">
         <v>0.01</v>
       </c>
       <c r="H10" s="6">
-        <v>0.43572755479480257</v>
+        <v>0.43729616908896429</v>
       </c>
       <c r="I10" s="6">
-        <v>0.43737034395009322</v>
+        <v>0.44091490823207902</v>
       </c>
       <c r="J10" s="6">
-        <v>0.46113800315406173</v>
+        <v>0.44859508462953768</v>
       </c>
       <c r="K10" s="6">
-        <v>0.45646978490952539</v>
+        <v>0.44349607374530559</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>16</v>
@@ -3112,63 +3131,276 @@
         <v>4</v>
       </c>
       <c r="E11" s="6">
-        <v>32</v>
-      </c>
-      <c r="F11" s="6">
-        <v>5.0000000000000002E-5</v>
+        <v>16</v>
+      </c>
+      <c r="F11" s="7">
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="G11" s="6">
         <v>0.01</v>
       </c>
       <c r="H11" s="6">
-        <v>0.42282602623570131</v>
+        <v>0.42420684743682457</v>
       </c>
       <c r="I11" s="6">
-        <v>0.42303761452812361</v>
+        <v>0.42592016793038268</v>
       </c>
       <c r="J11" s="6">
-        <v>0.43202268431307123</v>
+        <v>0.44397123742230621</v>
       </c>
       <c r="K11" s="6">
-        <v>0.42813246841925567</v>
+        <v>0.43871628542164559</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <v>3.0000000000000001E-5</v>
       </c>
       <c r="G12" s="6">
         <v>0.01</v>
       </c>
       <c r="H12" s="6">
+        <v>0.43572755479480257</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0.43737034395009322</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0.46113800315406173</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0.45646978490952539</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="6">
+        <v>4</v>
+      </c>
+      <c r="E13" s="6">
+        <v>8</v>
+      </c>
+      <c r="F13" s="7">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0.44289955772203538</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0.44575372275589992</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0.47196292752672248</v>
+      </c>
+      <c r="K13" s="6">
+        <v>0.46602936155684532</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="6">
+        <v>4</v>
+      </c>
+      <c r="E14" s="6">
+        <v>16</v>
+      </c>
+      <c r="F14" s="7">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0.4437670401715425</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0.45009632056679161</v>
+      </c>
+      <c r="J14" s="6">
+        <v>0.48112682006142371</v>
+      </c>
+      <c r="K14" s="6">
+        <v>0.47490611130078519</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="6">
+        <v>4</v>
+      </c>
+      <c r="E15" s="6">
+        <v>32</v>
+      </c>
+      <c r="F15" s="7">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0.4331810894028158</v>
+      </c>
+      <c r="I15" s="6">
+        <v>0.4346421876790667</v>
+      </c>
+      <c r="J15" s="6">
+        <v>0.46313638106471139</v>
+      </c>
+      <c r="K15" s="6">
+        <v>0.4578354387162854</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="6">
+        <v>4</v>
+      </c>
+      <c r="E16" s="6">
+        <v>8</v>
+      </c>
+      <c r="F16" s="7">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H16" s="6">
+        <v>0.43615783648502032</v>
+      </c>
+      <c r="I16" s="6">
+        <v>0.43833040361883707</v>
+      </c>
+      <c r="J16" s="6">
+        <v>0.46344518856961381</v>
+      </c>
+      <c r="K16" s="6">
+        <v>0.45817685216797538</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="6">
+        <v>4</v>
+      </c>
+      <c r="E17" s="6">
+        <v>32</v>
+      </c>
+      <c r="F17" s="7">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0.42282602623570131</v>
+      </c>
+      <c r="I17" s="6">
+        <v>0.42303761452812361</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0.43202268431307123</v>
+      </c>
+      <c r="K17" s="6">
+        <v>0.42813246841925567</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="6">
+        <v>4</v>
+      </c>
+      <c r="E18" s="6">
+        <v>8</v>
+      </c>
+      <c r="F18" s="7">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="H18" s="6">
         <v>0.43165791366051121</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I18" s="6">
         <v>0.4330795209717142</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J18" s="6">
         <v>0.45850326738972208</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K18" s="6">
         <v>0.45339706384431538</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K19">
+    <sortCondition ref="A1:A19"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>